--- a/settings/data/Global.xlsx
+++ b/settings/data/Global.xlsx
@@ -29,39 +29,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>全局变量ID</t>
+  </si>
+  <si>
+    <t>中文名</t>
+  </si>
+  <si>
+    <t>变量值</t>
+  </si>
   <si>
     <t>备注</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>red_ufo_rate</t>
+  </si>
+  <si>
     <t>红碟经验倍率</t>
   </si>
   <si>
+    <t>green_ufo_rate</t>
+  </si>
+  <si>
     <t>绿碟符力倍率</t>
   </si>
   <si>
+    <t>blue_ufo_rate</t>
+  </si>
+  <si>
     <t>蓝碟分数倍率</t>
   </si>
   <si>
+    <t>blue_ufo_pv_coefficient</t>
+  </si>
+  <si>
     <t>蓝碟得点倍率系数</t>
   </si>
   <si>
     <t>蓝碟增加的得点倍率=该数值*收集到的记忆碎片数</t>
   </si>
   <si>
+    <t>red_ufo_weight</t>
+  </si>
+  <si>
     <t>红碟基础权重</t>
   </si>
   <si>
     <t>自机结晶槽全满、结晶全满级后不再出现红碟</t>
   </si>
   <si>
+    <t>green_ufo_weight</t>
+  </si>
+  <si>
     <t>绿碟基础权重</t>
   </si>
   <si>
+    <t>blue_ufo_weight</t>
+  </si>
+  <si>
     <t>蓝碟基础权重</t>
   </si>
   <si>
+    <t>colorful_ufo_weight</t>
+  </si>
+  <si>
     <t>彩碟基础权重</t>
+  </si>
+  <si>
+    <t>upgrade_exp_difference</t>
   </si>
   <si>
     <t>升级所需经验公差</t>
@@ -80,9 +131,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -553,139 +611,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -998,97 +1065,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="73.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="29.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="50.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="C1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="2" s="1" customFormat="1" ht="40.8" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
         <v>2</v>
       </c>
-      <c r="B3">
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>0.01</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
+      <c r="D8" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0.01</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
+      <c r="D12" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
